--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
@@ -60,6 +60,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -86,7 +93,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.000000_ "/>
   </numFmts>
   <fonts count="22">
     <font>

--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <r>
       <rPr>
@@ -78,9 +78,6 @@
       </rPr>
       <t>单位成本</t>
     </r>
-  </si>
-  <si>
-    <t>币种(默认CNY)</t>
   </si>
 </sst>
 </file>
@@ -1041,17 +1038,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1063,9 +1059,6 @@
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
       <rPr>
@@ -60,13 +60,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -76,8 +69,29 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>单位成本</t>
+      <t>材料成本</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>仓库</t>
+    </r>
+  </si>
+  <si>
+    <t>头程运费</t>
+  </si>
+  <si>
+    <t>清关税费</t>
   </si>
 </sst>
 </file>
@@ -1038,16 +1052,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="17.75" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1059,6 +1076,15 @@
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/inventorySkuCostDetailTemplate.xlsx
@@ -60,20 +60,13 @@
   </si>
   <si>
     <r>
-      <t>*</t>
-    </r>
-    <r>
       <rPr>
         <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>材料成本</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>*</t>
     </r>
     <r>
@@ -85,6 +78,27 @@
         <scheme val="minor"/>
       </rPr>
       <t>仓库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>材料成本</t>
     </r>
   </si>
   <si>
@@ -1058,8 +1072,8 @@
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="20.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.75" customWidth="1"/>
     <col min="7" max="7" width="16.875" customWidth="1"/>
   </cols>
@@ -1074,10 +1088,10 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
